--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -604,6 +604,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -613,7 +616,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -774,6 +777,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -817,7 +823,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -979,6 +985,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -988,7 +997,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1150,6 +1159,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1946497.5998595944</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1987254.1592249498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1192,7 +1204,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1354,6 +1366,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1363,7 +1378,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1525,6 +1540,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>597129.43630348239</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>637885.9956688378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1546,11 +1564,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="439701888"/>
-        <c:axId val="466713216"/>
+        <c:axId val="154700416"/>
+        <c:axId val="433496448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="439701888"/>
+        <c:axId val="154700416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1593,14 +1611,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466713216"/>
+        <c:crossAx val="433496448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466713216"/>
+        <c:axId val="433496448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1651,7 +1669,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="439701888"/>
+        <c:crossAx val="154700416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1812,7 +1830,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1974,6 +1992,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-31695.699802721694</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-41581.258082443448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1988,8 +2009,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="474833664"/>
-        <c:axId val="474495232"/>
+        <c:axId val="528384384"/>
+        <c:axId val="522732672"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2014,7 +2035,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2176,6 +2197,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2185,7 +2209,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2347,6 +2371,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2363,11 +2390,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469383808"/>
-        <c:axId val="474493312"/>
+        <c:axId val="437243264"/>
+        <c:axId val="447632896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469383808"/>
+        <c:axId val="437243264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2410,14 +2437,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474493312"/>
+        <c:crossAx val="447632896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="474493312"/>
+        <c:axId val="447632896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2468,12 +2495,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469383808"/>
+        <c:crossAx val="437243264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="474495232"/>
+        <c:axId val="522732672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2510,12 +2537,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474833664"/>
+        <c:crossAx val="528384384"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="474833664"/>
+        <c:axId val="528384384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2524,7 +2551,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="474495232"/>
+        <c:crossAx val="522732672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2933,7 +2960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5491,6 +5518,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:13" ht="12.75">
+      <c r="A57" s="11">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="12">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="12">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="13">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="13">
+        <v>-41581.258082443448</v>
+      </c>
+      <c r="F57" s="14">
+        <v>-39080.129391425355</v>
+      </c>
+      <c r="G57" s="14">
+        <v>1659106.4026916635</v>
+      </c>
+      <c r="H57" s="14">
+        <v>1765289.2298686488</v>
+      </c>
+      <c r="I57" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J57" s="14">
+        <v>1987254.1592249498</v>
+      </c>
+      <c r="K57" s="14">
+        <v>637885.9956688378</v>
+      </c>
+      <c r="L57" s="13">
+        <v>221964.92935630088</v>
+      </c>
+      <c r="M57" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -607,6 +607,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -616,7 +619,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -780,6 +783,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -823,7 +829,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -988,6 +994,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -997,7 +1006,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1162,6 +1171,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1987254.1592249498</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2000527.0373446848</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1204,7 +1216,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1369,6 +1381,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1378,7 +1393,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1543,6 +1558,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>637885.9956688378</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>651158.87378857285</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1564,11 +1582,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="154700416"/>
-        <c:axId val="433496448"/>
+        <c:axId val="409097344"/>
+        <c:axId val="493123840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="154700416"/>
+        <c:axId val="409097344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1611,14 +1629,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433496448"/>
+        <c:crossAx val="493123840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433496448"/>
+        <c:axId val="493123840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1669,7 +1687,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154700416"/>
+        <c:crossAx val="409097344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1830,7 +1848,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1995,6 +2013,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-41581.258082443448</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-45319.47395988238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2009,8 +2030,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="528384384"/>
-        <c:axId val="522732672"/>
+        <c:axId val="559777664"/>
+        <c:axId val="559776128"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2035,7 +2056,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2200,6 +2221,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2209,7 +2233,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2374,6 +2398,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2390,11 +2417,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437243264"/>
-        <c:axId val="447632896"/>
+        <c:axId val="557294336"/>
+        <c:axId val="557295872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437243264"/>
+        <c:axId val="557294336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2437,14 +2464,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447632896"/>
+        <c:crossAx val="557295872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447632896"/>
+        <c:axId val="557295872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2495,12 +2522,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437243264"/>
+        <c:crossAx val="557294336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522732672"/>
+        <c:axId val="559776128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2537,12 +2564,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528384384"/>
+        <c:crossAx val="559777664"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="528384384"/>
+        <c:axId val="559777664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2578,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522732672"/>
+        <c:crossAx val="559776128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2960,7 +2987,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5559,6 +5586,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:13" ht="12.75">
+      <c r="A58" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="12">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="12">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="13">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="13">
+        <v>-45319.47395988238</v>
+      </c>
+      <c r="F58" s="14">
+        <v>-42275.627640859449</v>
+      </c>
+      <c r="G58" s="14">
+        <v>1616830.775050804</v>
+      </c>
+      <c r="H58" s="14">
+        <v>1733242.6340285016</v>
+      </c>
+      <c r="I58" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J58" s="14">
+        <v>2000527.0373446848</v>
+      </c>
+      <c r="K58" s="14">
+        <v>651158.87378857285</v>
+      </c>
+      <c r="L58" s="13">
+        <v>267284.40331618325</v>
+      </c>
+      <c r="M58" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -610,6 +610,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -619,7 +622,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -786,6 +789,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -829,7 +835,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -997,6 +1003,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,7 +1015,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1174,6 +1183,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>2000527.0373446848</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2005377.5635922966</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1216,7 +1228,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1384,6 +1396,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1393,7 +1408,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1561,6 +1576,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>651158.87378857285</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>656009.40003618458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1582,11 +1600,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="409097344"/>
-        <c:axId val="493123840"/>
+        <c:axId val="79177216"/>
+        <c:axId val="79178752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="409097344"/>
+        <c:axId val="79177216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1629,14 +1647,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493123840"/>
+        <c:crossAx val="79178752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493123840"/>
+        <c:axId val="79178752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1687,7 +1705,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="409097344"/>
+        <c:crossAx val="79177216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1848,7 +1866,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2016,6 +2034,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-45319.47395988238</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-43530.43160834584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2030,8 +2051,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="559777664"/>
-        <c:axId val="559776128"/>
+        <c:axId val="397588736"/>
+        <c:axId val="397586816"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2056,7 +2077,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2224,6 +2245,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2233,7 +2257,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2401,6 +2425,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2417,11 +2444,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557294336"/>
-        <c:axId val="557295872"/>
+        <c:axId val="395286784"/>
+        <c:axId val="396994048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557294336"/>
+        <c:axId val="395286784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2464,14 +2491,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557295872"/>
+        <c:crossAx val="396994048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557295872"/>
+        <c:axId val="396994048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2522,12 +2549,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557294336"/>
+        <c:crossAx val="395286784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="559776128"/>
+        <c:axId val="397586816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2564,12 +2591,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559777664"/>
+        <c:crossAx val="397588736"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="559777664"/>
+        <c:axId val="397588736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,7 +2605,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559776128"/>
+        <c:crossAx val="397586816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2987,7 +3014,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5627,6 +5654,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:13" ht="12.75">
+      <c r="A59" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="12">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="12">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="13">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="13">
+        <v>-43530.43160834584</v>
+      </c>
+      <c r="F59" s="14">
+        <v>-40493.422955785085</v>
+      </c>
+      <c r="G59" s="14">
+        <v>1576337.3520950188</v>
+      </c>
+      <c r="H59" s="14">
+        <v>1694562.7286677675</v>
+      </c>
+      <c r="I59" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J59" s="14">
+        <v>2005377.5635922966</v>
+      </c>
+      <c r="K59" s="14">
+        <v>656009.40003618458</v>
+      </c>
+      <c r="L59" s="13">
+        <v>310814.83492452907</v>
+      </c>
+      <c r="M59" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -613,6 +613,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -622,7 +625,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -792,6 +795,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -835,7 +841,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1006,6 +1012,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1015,7 +1024,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1186,6 +1195,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>2005377.5635922966</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1962816.3453439225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1228,7 +1240,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1399,6 +1411,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1408,7 +1423,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1579,6 +1594,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>656009.40003618458</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>613448.18178781052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1600,11 +1618,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79177216"/>
-        <c:axId val="79178752"/>
+        <c:axId val="92161920"/>
+        <c:axId val="92163456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79177216"/>
+        <c:axId val="92161920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1647,14 +1665,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79178752"/>
+        <c:crossAx val="92163456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79178752"/>
+        <c:axId val="92163456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1705,7 +1723,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79177216"/>
+        <c:crossAx val="92161920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1866,7 +1884,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2037,6 +2055,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-43530.43160834584</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-34862.836718054765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2051,8 +2072,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="397588736"/>
-        <c:axId val="397586816"/>
+        <c:axId val="417353728"/>
+        <c:axId val="417241344"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2077,7 +2098,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2248,6 +2269,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2257,7 +2281,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2428,6 +2452,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2444,11 +2471,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395286784"/>
-        <c:axId val="396994048"/>
+        <c:axId val="393928064"/>
+        <c:axId val="395000832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395286784"/>
+        <c:axId val="393928064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2491,14 +2518,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="396994048"/>
+        <c:crossAx val="395000832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="396994048"/>
+        <c:axId val="395000832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2549,12 +2576,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395286784"/>
+        <c:crossAx val="393928064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="397586816"/>
+        <c:axId val="417241344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2591,12 +2618,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397588736"/>
+        <c:crossAx val="417353728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="397588736"/>
+        <c:axId val="417353728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2605,7 +2632,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="397586816"/>
+        <c:crossAx val="417241344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3014,7 +3041,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5695,6 +5722,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:13" ht="12.75">
+      <c r="A60" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="12">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="12">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="13">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="13">
+        <v>-34862.836718054765</v>
+      </c>
+      <c r="F60" s="14">
+        <v>-33266.066266917558</v>
+      </c>
+      <c r="G60" s="14">
+        <v>1543071.2858281012</v>
+      </c>
+      <c r="H60" s="14">
+        <v>1617138.6737013387</v>
+      </c>
+      <c r="I60" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J60" s="14">
+        <v>1962816.3453439225</v>
+      </c>
+      <c r="K60" s="14">
+        <v>613448.18178781052</v>
+      </c>
+      <c r="L60" s="13">
+        <v>345677.67164258385</v>
+      </c>
+      <c r="M60" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -616,6 +616,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -625,7 +628,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -798,6 +801,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -841,7 +847,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1015,6 +1021,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1024,7 +1033,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1198,6 +1207,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1962816.3453439225</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2161872.6456984566</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1240,7 +1252,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1414,6 +1426,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1423,7 +1438,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1597,6 +1612,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>613448.18178781052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>812504.48214234458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1618,11 +1636,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92161920"/>
-        <c:axId val="92163456"/>
+        <c:axId val="456073984"/>
+        <c:axId val="456075904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92161920"/>
+        <c:axId val="456073984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1665,14 +1683,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92163456"/>
+        <c:crossAx val="456075904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92163456"/>
+        <c:axId val="456075904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1723,7 +1741,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92161920"/>
+        <c:crossAx val="456073984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1884,7 +1902,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2058,6 +2076,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-34862.836718054765</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-65549.847565695833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2072,8 +2093,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="417353728"/>
-        <c:axId val="417241344"/>
+        <c:axId val="472214528"/>
+        <c:axId val="472212992"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2098,7 +2119,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2272,6 +2293,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2281,7 +2305,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2455,6 +2479,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2471,11 +2498,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="393928064"/>
-        <c:axId val="395000832"/>
+        <c:axId val="463889920"/>
+        <c:axId val="463891840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="393928064"/>
+        <c:axId val="463889920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2518,14 +2545,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395000832"/>
+        <c:crossAx val="463891840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395000832"/>
+        <c:axId val="463891840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2576,12 +2603,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393928064"/>
+        <c:crossAx val="463889920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="417241344"/>
+        <c:axId val="472212992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2618,12 +2645,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417353728"/>
+        <c:crossAx val="472214528"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="417353728"/>
+        <c:axId val="472214528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2632,7 +2659,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="417241344"/>
+        <c:crossAx val="472212992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3041,7 +3068,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5763,6 +5790,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:13" ht="12.75">
+      <c r="A61" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="12">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="12">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="13">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="13">
+        <v>-65549.847565695833</v>
+      </c>
+      <c r="F61" s="14">
+        <v>-55692.306725832073</v>
+      </c>
+      <c r="G61" s="14">
+        <v>1487378.979102269</v>
+      </c>
+      <c r="H61" s="14">
+        <v>1750645.1264901769</v>
+      </c>
+      <c r="I61" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J61" s="14">
+        <v>2161872.6456984566</v>
+      </c>
+      <c r="K61" s="14">
+        <v>812504.48214234458</v>
+      </c>
+      <c r="L61" s="13">
+        <v>411227.51920827967</v>
+      </c>
+      <c r="M61" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -619,6 +619,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -628,7 +631,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -804,6 +807,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -847,7 +853,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1024,6 +1030,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1033,7 +1042,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1210,6 +1219,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>2161872.6456984566</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2263014.35528298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1252,7 +1264,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1429,6 +1441,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1438,7 +1453,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1615,6 +1630,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>812504.48214234458</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>913646.19172686804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1636,11 +1654,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="456073984"/>
-        <c:axId val="456075904"/>
+        <c:axId val="99720192"/>
+        <c:axId val="103724160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="456073984"/>
+        <c:axId val="99720192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1683,14 +1701,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="456075904"/>
+        <c:crossAx val="103724160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="456075904"/>
+        <c:axId val="103724160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1741,7 +1759,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="456073984"/>
+        <c:crossAx val="99720192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1902,7 +1920,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2079,6 +2097,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-65549.847565695833</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-72114.733350567156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2093,8 +2114,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="472214528"/>
-        <c:axId val="472212992"/>
+        <c:axId val="401867904"/>
+        <c:axId val="399842304"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2119,7 +2140,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2296,6 +2317,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2305,7 +2329,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2482,6 +2506,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2498,11 +2525,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="463889920"/>
-        <c:axId val="463891840"/>
+        <c:axId val="399531392"/>
+        <c:axId val="399840384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="463889920"/>
+        <c:axId val="399531392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2545,14 +2572,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463891840"/>
+        <c:crossAx val="399840384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="463891840"/>
+        <c:axId val="399840384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2603,12 +2630,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463889920"/>
+        <c:crossAx val="399531392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="472212992"/>
+        <c:axId val="399842304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2645,12 +2672,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472214528"/>
+        <c:crossAx val="401867904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="472214528"/>
+        <c:axId val="401867904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2659,7 +2686,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="472212992"/>
+        <c:crossAx val="399842304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3068,7 +3095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5831,6 +5858,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:13" ht="12.75">
+      <c r="A62" s="11">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="12">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="12">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="13">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="13">
+        <v>-72114.733350567156</v>
+      </c>
+      <c r="F62" s="14">
+        <v>-57923.480381017253</v>
+      </c>
+      <c r="G62" s="14">
+        <v>1429455.4987212517</v>
+      </c>
+      <c r="H62" s="14">
+        <v>1779672.1027241333</v>
+      </c>
+      <c r="I62" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J62" s="14">
+        <v>2263014.35528298</v>
+      </c>
+      <c r="K62" s="14">
+        <v>913646.19172686804</v>
+      </c>
+      <c r="L62" s="13">
+        <v>483342.25255884684</v>
+      </c>
+      <c r="M62" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">
